--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0002_ses-01_WMprob_pdf.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0002_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -891,7 +892,7 @@
         <v>0.060350030175015036</v>
       </c>
       <c r="H22" s="0">
-        <v>0.47719138783161918</v>
+        <v>0.47719138783161919</v>
       </c>
       <c r="I22" s="0">
         <v>0.66930150344580985</v>
@@ -926,7 +927,7 @@
         <v>0.4220791034457661</v>
       </c>
       <c r="G23" s="0">
-        <v>0.32186682760008017</v>
+        <v>0.32186682760008018</v>
       </c>
       <c r="H23" s="0">
         <v>0.76123388058853536</v>
@@ -1321,7 +1322,7 @@
         <v>5.2835051546391707</v>
       </c>
       <c r="L33" s="0">
-        <v>3.8425652349702943</v>
+        <v>3.8425652349702944</v>
       </c>
     </row>
     <row r="34">
@@ -1344,7 +1345,7 @@
         <v>3.6859149292289746</v>
       </c>
       <c r="G34" s="0">
-        <v>3.1985515992757962</v>
+        <v>3.1985515992757963</v>
       </c>
       <c r="H34" s="0">
         <v>2.4086803385786495</v>
@@ -1528,7 +1529,7 @@
         <v>3.3683552520856845</v>
       </c>
       <c r="E39" s="0">
-        <v>3.2107163101524478</v>
+        <v>3.2107163101524479</v>
       </c>
       <c r="F39" s="0">
         <v>2.7471527853582192</v>
@@ -1701,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="L43" s="0">
-        <v>2.3372624638447403</v>
+        <v>2.3372624638447404</v>
       </c>
     </row>
     <row r="44">
@@ -1858,7 +1859,7 @@
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>2.1315349020380014</v>
+        <v>2.1315349020380015</v>
       </c>
       <c r="B48" s="0">
         <v>3.5087719298245581</v>
@@ -1885,7 +1886,7 @@
         <v>1.5352227363905371</v>
       </c>
       <c r="J48" s="0">
-        <v>1.7666543982333442</v>
+        <v>1.7666543982333443</v>
       </c>
       <c r="K48" s="0">
         <v>0.12886597938144317</v>
@@ -1952,7 +1953,7 @@
         <v>1.6774005749008463</v>
       </c>
       <c r="G50" s="0">
-        <v>2.2530677932005609</v>
+        <v>2.253067793200561</v>
       </c>
       <c r="H50" s="0">
         <v>1.9712548997329982</v>
@@ -2010,7 +2011,7 @@
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>1.6663384857733567</v>
+        <v>1.6663384857733568</v>
       </c>
       <c r="B52" s="0">
         <v>0.87719298245613953</v>
@@ -2338,7 +2339,7 @@
         <v>1.1304891211725263</v>
       </c>
       <c r="I60" s="0">
-        <v>0.6772457349407156</v>
+        <v>0.67724573494071561</v>
       </c>
       <c r="J60" s="0">
         <v>0.97534044902465866</v>
@@ -2399,10 +2400,10 @@
         <v>0.74817078583294172</v>
       </c>
       <c r="D62" s="0">
-        <v>0.44719063303921291</v>
+        <v>0.44719063303921292</v>
       </c>
       <c r="E62" s="0">
-        <v>1.0907246636236156</v>
+        <v>1.0907246636236157</v>
       </c>
       <c r="F62" s="0">
         <v>0.88600225594003479</v>
@@ -2446,7 +2447,7 @@
         <v>0.92784630498853748</v>
       </c>
       <c r="G63" s="0">
-        <v>0.98571715952524563</v>
+        <v>0.98571715952524564</v>
       </c>
       <c r="H63" s="0">
         <v>0.93734022609782341</v>
@@ -2604,7 +2605,7 @@
         <v>0.64761688348576885</v>
       </c>
       <c r="I67" s="0">
-        <v>0.44289090584099577</v>
+        <v>0.44289090584099578</v>
       </c>
       <c r="J67" s="0">
         <v>0.55207949944792001</v>
@@ -2639,7 +2640,7 @@
         <v>0.80466706900020035</v>
       </c>
       <c r="H68" s="0">
-        <v>0.67602113276146047</v>
+        <v>0.67602113276146048</v>
       </c>
       <c r="I68" s="0">
         <v>0.30585291255387154</v>
@@ -2689,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="0">
-        <v>0.55671321494106873</v>
+        <v>0.55671321494106874</v>
       </c>
     </row>
     <row r="70">
@@ -2776,7 +2777,7 @@
         <v>0.17543859649122792</v>
       </c>
       <c r="C72" s="0">
-        <v>0.28024702316793237</v>
+        <v>0.28024702316793238</v>
       </c>
       <c r="D72" s="0">
         <v>0.18512730507537309</v>
@@ -2937,13 +2938,13 @@
         <v>0.2500074584563976</v>
       </c>
       <c r="F76" s="0">
-        <v>0.32565585998617302</v>
+        <v>0.32565585998617303</v>
       </c>
       <c r="G76" s="0">
         <v>0.34198350432508523</v>
       </c>
       <c r="H76" s="0">
-        <v>0.3124467420326078</v>
+        <v>0.31244674203260781</v>
       </c>
       <c r="I76" s="0">
         <v>0.1390240511608507</v>
@@ -3010,7 +3011,7 @@
         <v>0.079340273603731332</v>
       </c>
       <c r="E78" s="0">
-        <v>0.15394254005191071</v>
+        <v>0.15394254005191072</v>
       </c>
       <c r="F78" s="0">
         <v>0.21831677764436178</v>
@@ -3069,7 +3070,7 @@
         <v>0.12886597938144317</v>
       </c>
       <c r="L79" s="0">
-        <v>0.1570615494666126</v>
+        <v>0.15706154946661261</v>
       </c>
     </row>
     <row r="80">
@@ -3209,7 +3210,7 @@
         <v>0.060350030175015036</v>
       </c>
       <c r="H83" s="0">
-        <v>0.079531897971936535</v>
+        <v>0.079531897971936536</v>
       </c>
       <c r="I83" s="0">
         <v>0.033762983853349457</v>
@@ -3454,7 +3455,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B90" s="0">
         <v>0</v>
@@ -3492,7 +3493,7 @@
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B91" s="0">
         <v>0</v>
